--- a/diseases/d045/2005-2009.xlsx
+++ b/diseases/d045/2005-2009.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1309,9 +1306,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1853,9 +1847,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -2249,9 +2240,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -2793,9 +2781,6 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -3189,9 +3174,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -3733,9 +3715,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -4129,9 +4108,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -4673,9 +4649,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -5069,9 +5042,6 @@
       <c r="O25" t="n">
         <v>1</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.02163039537767103</v>
       </c>
@@ -5613,9 +5583,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -6009,9 +5976,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -6553,9 +6517,6 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -6949,9 +6910,6 @@
       <c r="O35" t="n">
         <v>2</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.04326079075534206</v>
       </c>
@@ -7493,9 +7451,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -7889,9 +7844,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -8433,9 +8385,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -8829,9 +8778,6 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -9373,9 +9319,6 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
@@ -9769,9 +9712,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -10313,9 +10253,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -10709,9 +10646,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -11253,9 +11187,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -11649,9 +11580,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -12193,9 +12121,6 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -12589,9 +12514,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -13133,9 +13055,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -13529,9 +13448,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -14073,9 +13989,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -14469,9 +14382,6 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -15013,9 +14923,6 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
@@ -15409,9 +15316,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -15953,9 +15857,6 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -16349,9 +16250,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -16893,9 +16791,6 @@
       <c r="O88" t="n">
         <v>1</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.01898885667429354</v>
       </c>
@@ -17289,9 +17184,6 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
@@ -17833,9 +17725,6 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
@@ -18229,9 +18118,6 @@
       <c r="O95" t="n">
         <v>1</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.02145695284662956</v>
       </c>
@@ -18773,9 +18659,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -19169,9 +19052,6 @@
       <c r="O100" t="n">
         <v>1</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.02145695284662956</v>
       </c>
@@ -19713,9 +19593,6 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -20109,9 +19986,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
@@ -20653,9 +20527,6 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
@@ -21049,9 +20920,6 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
@@ -21593,9 +21461,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -21989,9 +21854,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -22533,9 +22395,6 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
@@ -22929,9 +22788,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -23473,9 +23329,6 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
@@ -23869,9 +23722,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -24413,9 +24263,6 @@
       <c r="O128" t="n">
         <v>0</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0</v>
       </c>
@@ -24809,9 +24656,6 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0</v>
       </c>
@@ -25353,9 +25197,6 @@
       <c r="O133" t="n">
         <v>0</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0</v>
       </c>
@@ -25749,9 +25590,6 @@
       <c r="O135" t="n">
         <v>0</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0</v>
       </c>
@@ -26293,9 +26131,6 @@
       <c r="O138" t="n">
         <v>0</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0</v>
       </c>
@@ -26689,9 +26524,6 @@
       <c r="O140" t="n">
         <v>0</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0</v>
       </c>
@@ -27233,9 +27065,6 @@
       <c r="O143" t="n">
         <v>1</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0.01890820256735574</v>
       </c>
@@ -27629,9 +27458,6 @@
       <c r="O145" t="n">
         <v>0</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0</v>
       </c>
@@ -28173,9 +27999,6 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0</v>
       </c>
@@ -28569,9 +28392,6 @@
       <c r="O150" t="n">
         <v>0</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0</v>
       </c>
@@ -29113,9 +28933,6 @@
       <c r="O153" t="n">
         <v>0</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0</v>
       </c>
@@ -29509,9 +29326,6 @@
       <c r="O155" t="n">
         <v>2</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0.04247177219840264</v>
       </c>
@@ -30053,9 +29867,6 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0</v>
       </c>
@@ -30449,9 +30260,6 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0</v>
       </c>
@@ -30993,9 +30801,6 @@
       <c r="O163" t="n">
         <v>0</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0</v>
       </c>
@@ -31389,9 +31194,6 @@
       <c r="O165" t="n">
         <v>0</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0</v>
       </c>
@@ -31933,9 +31735,6 @@
       <c r="O168" t="n">
         <v>0</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0</v>
       </c>
@@ -32329,9 +32128,6 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0</v>
       </c>
@@ -32873,9 +32669,6 @@
       <c r="O173" t="n">
         <v>0</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0</v>
       </c>
@@ -33269,9 +33062,6 @@
       <c r="O175" t="n">
         <v>0</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0</v>
       </c>
@@ -33813,9 +33603,6 @@
       <c r="O178" t="n">
         <v>0</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0</v>
       </c>
@@ -34209,9 +33996,6 @@
       <c r="O180" t="n">
         <v>0</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0</v>
       </c>
@@ -34753,9 +34537,6 @@
       <c r="O183" t="n">
         <v>1</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0.01882042249213636</v>
       </c>
@@ -35149,9 +34930,6 @@
       <c r="O185" t="n">
         <v>0</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0</v>
       </c>
@@ -35693,9 +35471,6 @@
       <c r="O188" t="n">
         <v>0</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0</v>
       </c>
@@ -36089,9 +35864,6 @@
       <c r="O190" t="n">
         <v>1</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0.02097271009989092</v>
       </c>
@@ -36633,9 +36405,6 @@
       <c r="O193" t="n">
         <v>0</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0</v>
       </c>
@@ -37029,9 +36798,6 @@
       <c r="O195" t="n">
         <v>0</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>0</v>
       </c>
@@ -37573,9 +37339,6 @@
       <c r="O198" t="n">
         <v>0</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0</v>
       </c>
@@ -37969,9 +37732,6 @@
       <c r="O200" t="n">
         <v>0</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0</v>
       </c>
@@ -38513,9 +38273,6 @@
       <c r="O203" t="n">
         <v>0</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="R203" t="n">
         <v>0</v>
       </c>
@@ -38909,9 +38666,6 @@
       <c r="O205" t="n">
         <v>0</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>0</v>
       </c>
@@ -39453,9 +39207,6 @@
       <c r="O208" t="n">
         <v>0</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0</v>
       </c>
@@ -39849,9 +39600,6 @@
       <c r="O210" t="n">
         <v>0</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0</v>
       </c>
@@ -40393,9 +40141,6 @@
       <c r="O213" t="n">
         <v>0</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0</v>
       </c>
@@ -40789,9 +40534,6 @@
       <c r="O215" t="n">
         <v>1</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0.02097271009989092</v>
       </c>
@@ -41333,9 +41075,6 @@
       <c r="O218" t="n">
         <v>0</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0</v>
       </c>
@@ -41729,9 +41468,6 @@
       <c r="O220" t="n">
         <v>0</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>0</v>
       </c>
@@ -42273,9 +42009,6 @@
       <c r="O223" t="n">
         <v>0</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>0</v>
       </c>
@@ -42669,9 +42402,6 @@
       <c r="O225" t="n">
         <v>0</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>0</v>
       </c>
@@ -43213,9 +42943,6 @@
       <c r="O228" t="n">
         <v>0</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0</v>
       </c>
@@ -43609,9 +43336,6 @@
       <c r="O230" t="n">
         <v>0</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0</v>
       </c>
@@ -44153,9 +43877,6 @@
       <c r="O233" t="n">
         <v>0</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="R233" t="n">
         <v>0</v>
       </c>
@@ -44549,9 +44270,6 @@
       <c r="O235" t="n">
         <v>1</v>
       </c>
-      <c r="Q235" t="n">
-        <v>0</v>
-      </c>
       <c r="R235" t="n">
         <v>0.02097271009989092</v>
       </c>
@@ -45093,9 +44811,6 @@
       <c r="O238" t="n">
         <v>0</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0</v>
       </c>
@@ -45489,9 +45204,6 @@
       <c r="O240" t="n">
         <v>0</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="R240" t="n">
         <v>0</v>
       </c>
@@ -46033,9 +45745,6 @@
       <c r="O243" t="n">
         <v>0</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="R243" t="n">
         <v>0</v>
       </c>
@@ -46429,9 +46138,6 @@
       <c r="O245" t="n">
         <v>0</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>0</v>
       </c>
@@ -46973,9 +46679,6 @@
       <c r="O248" t="n">
         <v>1</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0.01873060270490507</v>
       </c>
@@ -47369,9 +47072,6 @@
       <c r="O250" t="n">
         <v>0</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
       <c r="R250" t="n">
         <v>0</v>
       </c>
@@ -47913,9 +47613,6 @@
       <c r="O253" t="n">
         <v>0</v>
       </c>
-      <c r="Q253" t="n">
-        <v>0</v>
-      </c>
       <c r="R253" t="n">
         <v>0</v>
       </c>
@@ -48309,9 +48006,6 @@
       <c r="O255" t="n">
         <v>0</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0</v>
       </c>
@@ -48853,9 +48547,6 @@
       <c r="O258" t="n">
         <v>0</v>
       </c>
-      <c r="Q258" t="n">
-        <v>0</v>
-      </c>
       <c r="R258" t="n">
         <v>0</v>
       </c>
@@ -49249,9 +48940,6 @@
       <c r="O260" t="n">
         <v>0</v>
       </c>
-      <c r="Q260" t="n">
-        <v>0</v>
-      </c>
       <c r="R260" t="n">
         <v>0</v>
       </c>
@@ -49793,9 +49481,6 @@
       <c r="O263" t="n">
         <v>0</v>
       </c>
-      <c r="Q263" t="n">
-        <v>0</v>
-      </c>
       <c r="R263" t="n">
         <v>0</v>
       </c>
@@ -50189,9 +49874,6 @@
       <c r="O265" t="n">
         <v>0</v>
       </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="R265" t="n">
         <v>0</v>
       </c>
@@ -50733,9 +50415,6 @@
       <c r="O268" t="n">
         <v>0</v>
       </c>
-      <c r="Q268" t="n">
-        <v>0</v>
-      </c>
       <c r="R268" t="n">
         <v>0</v>
       </c>
@@ -51129,9 +50808,6 @@
       <c r="O270" t="n">
         <v>0</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="R270" t="n">
         <v>0</v>
       </c>
@@ -51673,9 +51349,6 @@
       <c r="O273" t="n">
         <v>0</v>
       </c>
-      <c r="Q273" t="n">
-        <v>0</v>
-      </c>
       <c r="R273" t="n">
         <v>0</v>
       </c>
@@ -52069,9 +51742,6 @@
       <c r="O275" t="n">
         <v>2</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>0.04141968025042339</v>
       </c>
@@ -52613,9 +52283,6 @@
       <c r="O278" t="n">
         <v>0</v>
       </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
       <c r="R278" t="n">
         <v>0</v>
       </c>
@@ -53009,9 +52676,6 @@
       <c r="O280" t="n">
         <v>0</v>
       </c>
-      <c r="Q280" t="n">
-        <v>0</v>
-      </c>
       <c r="R280" t="n">
         <v>0</v>
       </c>
@@ -53553,9 +53217,6 @@
       <c r="O283" t="n">
         <v>0</v>
       </c>
-      <c r="Q283" t="n">
-        <v>0</v>
-      </c>
       <c r="R283" t="n">
         <v>0</v>
       </c>
@@ -53949,9 +53610,6 @@
       <c r="O285" t="n">
         <v>1</v>
       </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
       <c r="R285" t="n">
         <v>0.0207098401252117</v>
       </c>
@@ -54493,9 +54151,6 @@
       <c r="O288" t="n">
         <v>0</v>
       </c>
-      <c r="Q288" t="n">
-        <v>0</v>
-      </c>
       <c r="R288" t="n">
         <v>0</v>
       </c>
@@ -54889,9 +54544,6 @@
       <c r="O290" t="n">
         <v>0</v>
       </c>
-      <c r="Q290" t="n">
-        <v>0</v>
-      </c>
       <c r="R290" t="n">
         <v>0</v>
       </c>
@@ -55433,9 +55085,6 @@
       <c r="O293" t="n">
         <v>0</v>
       </c>
-      <c r="Q293" t="n">
-        <v>0</v>
-      </c>
       <c r="R293" t="n">
         <v>0</v>
       </c>
@@ -55829,9 +55478,6 @@
       <c r="O295" t="n">
         <v>1</v>
       </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
       <c r="R295" t="n">
         <v>0.0207098401252117</v>
       </c>
@@ -56373,9 +56019,6 @@
       <c r="O298" t="n">
         <v>0</v>
       </c>
-      <c r="Q298" t="n">
-        <v>0</v>
-      </c>
       <c r="R298" t="n">
         <v>0</v>
       </c>
@@ -56767,9 +56410,6 @@
         <v>0</v>
       </c>
       <c r="O300" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q300" t="n">
         <v>0</v>
       </c>
       <c r="R300" t="n">
